--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -468,16 +468,16 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-0.008136331686768861</v>
+        <v>0.07205250133794339</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.01392720799600422</v>
+        <v>0.09589980380594532</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2585959930934046</v>
+        <v>0.2276899671353446</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.2220214809549107</v>
+        <v>0.1975991461585894</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.03554973221252073</v>
+        <v>0.3931806074513031</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.05013938753748072</v>
+        <v>0.5752426864737616</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.1477561052641017</v>
+        <v>0.5725494911967176</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1444416510478904</v>
+        <v>0.1479184335623465</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1234846993044006</v>
+        <v>0.1054956006326827</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>-0.06362114960750904</v>
+        <v>0.5529825458629986</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>26.80553460497348</v>
+        <v>20.07757337269401</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.1687764454806914</v>
+        <v>-0.120894674973653</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.07334624229655273</v>
+        <v>0.1351752390433527</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.2095020986154231</v>
+        <v>0.1629855881030272</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.193789296896073</v>
+        <v>0.1642371441406718</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8855838415191262</v>
+        <v>-0.8332643322380711</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.25636467830659</v>
+        <v>-1.150606757083557</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.3805270377345072</v>
+        <v>0.7517401973930693</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.2221973154930725</v>
+        <v>0.1494730243073987</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.123069030532424</v>
+        <v>0.09258648760226473</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.7880460749154664</v>
+        <v>-0.8400375125611372</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>23.64435153851074</v>
+        <v>17.03088687955057</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.04729595454770774</v>
+        <v>-0.1037947874237893</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.07549298829909157</v>
+        <v>0.01171232220938134</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.2242332765369639</v>
+        <v>0.1556510234699751</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1992837501385203</v>
+        <v>0.1360387902100354</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.1802733644187545</v>
+        <v>-0.7509416531217954</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-0.2748674994648098</v>
+        <v>-1.023317001633819</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.4594209215724494</v>
+        <v>0.1109505194883476</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.219177697264535</v>
+        <v>0.2102129864595776</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.09586915897538872</v>
+        <v>0.08494798864530317</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.2244820610986257</v>
+        <v>-0.513022232679708</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>24.16335261330402</v>
+        <v>18.34719262692357</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-0.1082862498279542</v>
+        <v>0.0194673855187304</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.210738091686126</v>
+        <v>-0.09766247968809749</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2277122664442515</v>
+        <v>0.2055359417422368</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1728701727051089</v>
+        <v>0.1293900894144042</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-0.4761986417475667</v>
+        <v>0.1257745411971383</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-0.6772330254275875</v>
+        <v>0.214286057943074</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-1.424717539261724</v>
+        <v>-0.8656281699233386</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.2543453918511731</v>
+        <v>0.1838873673622461</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.3181028004006222</v>
+        <v>0.1862828629401598</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-0.4423094931487955</v>
+        <v>0.1102845001708394</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>25.13416560362749</v>
+        <v>18.07529702064885</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.3831538214712369</v>
+        <v>0.2009643345313394</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1297319833655042</v>
+        <v>-0.01907669375618914</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2735106536713666</v>
+        <v>0.2009322358920782</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1959520492680712</v>
+        <v>0.1176933461071618</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.312773552939729</v>
+        <v>0.9717557932915294</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.918438637632214</v>
+        <v>1.388218235837097</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.7651730844540847</v>
+        <v>-0.1177913179875855</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1788809932126184</v>
+        <v>0.13407018818028</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1572904223600189</v>
+        <v>0.1106941773725788</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.235400400228381</v>
+        <v>1.559910113098931</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>28.30431651034565</v>
+        <v>21.93286727180707</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.09576438231743678</v>
+        <v>0.1560168122811201</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1124979473425898</v>
+        <v>0.1736705002551351</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.4111557735027457</v>
+        <v>0.2647650641122575</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.3424083644986405</v>
+        <v>0.1980103754952919</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.5766216094043661</v>
+        <v>1.076494904366355</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.7857300264090272</v>
+        <v>1.490721404395836</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.7400668230223487</v>
+        <v>1.521849591341129</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.2282479227630851</v>
+        <v>0.1061370979197397</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1990018837052789</v>
+        <v>0.09129151738879848</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7963001017598423</v>
+        <v>2.855748008350402</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>27.96437867725325</v>
+        <v>20.64667586642173</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
+++ b/outputs/etf_trend_strategy/threshold_0.9/backtests/window_15/return_vol/post_rank_positive_return_rsi_bias_filter/staggered_7d/rsi_7_gt_60__bias_15_gt_-0.02/next_day_vwap/next_day_vwap_annual_metrics.xlsx
@@ -471,13 +471,13 @@
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="21" customWidth="1" min="12" max="12"/>
-    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -560,43 +560,43 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>0.07205250133794339</v>
+        <v>-0.03225405932102443</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>-0.02176047699359285</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0.09589980380594532</v>
+        <v>-0.0107270071190565</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.2276899671353446</v>
+        <v>0.2588577347073143</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0.1975991461585894</v>
+        <v>0.2460931391722982</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>0.3931806074513031</v>
+        <v>-0.07168385229300052</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.5752426864737616</v>
+        <v>-0.1018452608478569</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>0.5725494911967176</v>
+        <v>0.02054543821298636</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1479184335623465</v>
+        <v>0.1885924932295842</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0.1506490308477421</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1054956006326827</v>
+        <v>0.1796897552756022</v>
       </c>
       <c r="M2" s="4" t="n">
-        <v>0.5529825458629986</v>
+        <v>-0.1928569139307081</v>
       </c>
       <c r="N2" s="5" t="n">
-        <v>20.07757337269401</v>
+        <v>21.0442257963668</v>
       </c>
     </row>
     <row r="3">
@@ -606,43 +606,43 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.120894674973653</v>
+        <v>-0.1587735341016066</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>-0.2255774308756096</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.1351752390433527</v>
+        <v>0.08626284852407395</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.1629855881030272</v>
+        <v>0.2006661279655793</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0.1642371441406718</v>
+        <v>0.1900298253051732</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-0.8332643322380711</v>
+        <v>-0.8710942505449208</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-1.150606757083557</v>
+        <v>-1.188037772907482</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>0.7517401973930693</v>
+        <v>0.4445335352231871</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1494730243073987</v>
+        <v>0.227756442611062</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>0.2845881262232945</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.09258648760226473</v>
+        <v>0.1227573651945477</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-0.8400375125611372</v>
+        <v>-0.7234138749657355</v>
       </c>
       <c r="N3" s="5" t="n">
-        <v>17.03088687955057</v>
+        <v>18.02797172792807</v>
       </c>
     </row>
     <row r="4">
@@ -652,43 +652,43 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.1037947874237893</v>
+        <v>-0.1215180348097434</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>-0.1141699148043651</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.01171232220938134</v>
+        <v>-0.008295179999171398</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1556510234699751</v>
+        <v>0.1678803298992656</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>0.1360387902100354</v>
+        <v>0.1451212800759987</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-0.7509416531217954</v>
+        <v>-0.8083377055372329</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1.023317001633819</v>
+        <v>-1.105742841770783</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>0.1109505194883476</v>
+        <v>-0.02567224706564602</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.2102129864595776</v>
+        <v>0.2079405881103</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0.2177913835362562</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.08494798864530317</v>
+        <v>0.06738067895496891</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-0.513022232679708</v>
+        <v>-0.606945525846717</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>18.34719262692357</v>
+        <v>17.14583658116327</v>
       </c>
     </row>
     <row r="5">
@@ -698,43 +698,43 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.0194673855187304</v>
+        <v>-0.07167330258640092</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0.1298071537204202</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-0.09766247968809749</v>
+        <v>-0.1783317229346196</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>0.2055359417422368</v>
+        <v>0.2087854892739474</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.1293900894144042</v>
+        <v>0.1502391982477574</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.1257745411971383</v>
+        <v>-0.3386266316197784</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>0.214286057943074</v>
+        <v>-0.493262906811008</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-0.8656281699233386</v>
+        <v>-1.388154519422808</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1838873673622461</v>
+        <v>0.2152078062357221</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>0.1515696200238076</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1862828629401598</v>
+        <v>0.2774059008423543</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>0.1102845001708394</v>
+        <v>-0.3462786173503197</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>18.07529702064885</v>
+        <v>18.22231777999599</v>
       </c>
     </row>
     <row r="6">
@@ -744,43 +744,43 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.2009643345313394</v>
+        <v>0.09377413878925656</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0.2243203183030871</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-0.01907669375618914</v>
+        <v>-0.1066274712280925</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0.2009322358920782</v>
+        <v>0.159720192588646</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0.1176933461071618</v>
+        <v>0.1185744681621729</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.9717557932915294</v>
+        <v>0.5687330751569581</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.388218235837097</v>
+        <v>0.769019455870035</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.1177913179875855</v>
+        <v>-0.9975348334356721</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.13407018818028</v>
+        <v>0.0930603468698229</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0.1188658802983931</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1106941773725788</v>
+        <v>0.1988242054348842</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>1.559910113098931</v>
+        <v>1.046753771041522</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>21.93286727180707</v>
+        <v>19.03940271742799</v>
       </c>
     </row>
     <row r="7">
@@ -790,43 +790,43 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.1560168122811201</v>
+        <v>0.1014232512171223</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>-0.01504143451691176</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.1736705002551351</v>
+        <v>0.1182432335891308</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.2647650641122575</v>
+        <v>0.289306860418966</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.1980103754952919</v>
+        <v>0.2615633196993575</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1.076494904366355</v>
+        <v>0.7031019763804484</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.490721404395836</v>
+        <v>0.9798340976123024</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1.521849591341129</v>
+        <v>0.8400871813804029</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.1061370979197397</v>
+        <v>0.1533571156446626</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>0.127969093077366</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.09129151738879848</v>
+        <v>0.138711587129642</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.855748008350402</v>
+        <v>1.257992608840784</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>20.64667586642173</v>
+        <v>22.97859008282287</v>
       </c>
     </row>
   </sheetData>
